--- a/data/evaluation/instances/instance_evaluation_0.xlsx
+++ b/data/evaluation/instances/instance_evaluation_0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mathieu/Documents/Work/PhD Years/PhD/Code/XWSRP/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D009CEC-E59C-4640-B44B-458896F3A3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E5363D-3A44-904A-B185-7023D2A75F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="460" windowWidth="28800" windowHeight="16660" activeTab="2" xr2:uid="{745759C5-7123-8144-B92E-2C75C62BB0A9}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="16660" activeTab="2" xr2:uid="{745759C5-7123-8144-B92E-2C75C62BB0A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="117">
   <si>
     <t>Latitude</t>
   </si>
@@ -385,6 +385,9 @@
   </si>
   <si>
     <t>12:30pm</t>
+  </si>
+  <si>
+    <t>2:00pm</t>
   </si>
 </sst>
 </file>
@@ -1365,7 +1368,7 @@
         <v>23</v>
       </c>
       <c r="H18" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
